--- a/excel/output.xlsx
+++ b/excel/output.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,27 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -446,234 +425,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>MonCal.Facts.RF</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="n"/>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CTRL</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>DomKldg</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
           <t>MonCal.Facts.DC</t>
         </is>
       </c>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>MonCal.Interpret</t>
         </is>
       </c>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>StratKldg</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>BDS.Emotions</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>MotOrient.Value</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>justification</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>justification</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>justification</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>justification</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>justification</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>justification</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>justification</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>justification</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t>justification</t>
-        </is>
-      </c>
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Il y a eu beaucoup de réponse incorrecte et pas mal d'ignorance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cela révèle que je ne suis pas sûr de mes réponses</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pour espérer davantage au prochain test il va falloir que je révise plus ce qui me permettra d'avoir de l'assurance et de la justesse dans mes réponses</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Grâce à ces tests je vois qu'il faut que je m'améliore en mécanique car je n'ai pas du tout compris. J'ai beaucoup d'ignorance car je ne connais pas bien ma leçon. Je me sens plus à l'aise en chimie, mais je confonds encore beaucoup stéréoisomère, énantiomère, de configuration, de conformation . . . J'ai aussi besoin de revoir les titrages car je n'arrive pas à faire les calculs.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1 réponse dangereuse</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>je préfère ne pas me risquer à dire que c'est juste si ça peut ne pas l'être</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Grâce à ces tests je vois qu'il faut que je m'améliore en mécanique car je n'ai pas du tout compris. J'ai beaucoup d'ignorance car je ne connais pas bien ma leçon. Je me sens plus à l'aise en chimie, mais je confonds encore beaucoup stéréoisomère, énantiomère, de configuration, de conformation . . . J'ai aussi besoin de revoir les titrages car je n'arrive pas à faire les calculs.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pour espérer davantage au prochain test il va falloir que je révise plus ce qui me permettra d'avoir de l'assurance et de la justesse dans mes réponses</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ce sont des chapitres que je n'ai pas encore bien révisé surtout la chimie.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Il y a eu beaucoup de réponse incorrecte et pas mal d'ignorance</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Cela révèle que je ne suis pas sûr de mes réponses</t>
-        </is>
-      </c>
+          <t>Il y a 6 réponses incorrectes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Généralement pas sur de moi</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Pour espérer davantage au prochain test il va falloir que je révise plus ce qui me permettra d'avoir de l'assurance et de la justesse dans mes réponses</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Grâce à ces tests je vois qu'il faut que je m'améliore en mécanique car je n'ai pas du tout compris. J'ai beaucoup d'ignorance car je ne connais pas bien ma leçon. Je me sens plus à l'aise en chimie, mais je confonds encore beaucoup stéréoisomère, énantiomère, de configuration, de conformation . . . J'ai aussi besoin de revoir les titrages car je n'arrive pas à faire les calculs.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1 réponse dangereuse</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>je préfère ne pas me risquer à dire que c'est juste si ça peut ne pas l'être</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Score attribué au fait que je n'étais pas assez attentive et concentrée lors du test.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>je n'étais pas très concentrée</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>le commentaire peut indiquer une émotion ressentie pendant le test, mais également une stratégie dapprentissage utilisée</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Toutefois, cela permet très certainement de cibler les points faibles. Le test est toujours utile.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>19/32 réponses correctes, peu d'ignorance (2).</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>